--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/51.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/51.xlsx
@@ -426,13 +426,13 @@
         <v>-23.40256740568942</v>
       </c>
       <c r="E2">
-        <v>-11.47060409576658</v>
+        <v>-18.56816292052047</v>
       </c>
       <c r="F2">
-        <v>-0.3928177682268529</v>
+        <v>-0.7452044330103598</v>
       </c>
       <c r="G2">
-        <v>-12.64416636153913</v>
+        <v>-16.02415555931485</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-23.21979427591935</v>
       </c>
       <c r="E3">
-        <v>-12.54694085485768</v>
+        <v>-19.18506787763739</v>
       </c>
       <c r="F3">
-        <v>-0.8859233455609258</v>
+        <v>-0.9429191647105458</v>
       </c>
       <c r="G3">
-        <v>-12.95344414690893</v>
+        <v>-15.5757074052924</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.99218071937116</v>
       </c>
       <c r="E4">
-        <v>-10.7962780882324</v>
+        <v>-18.71305597486989</v>
       </c>
       <c r="F4">
-        <v>-0.9815318544572391</v>
+        <v>-0.5495481943061306</v>
       </c>
       <c r="G4">
-        <v>-12.35539078469405</v>
+        <v>-15.08260164721796</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.72223381783758</v>
       </c>
       <c r="E5">
-        <v>-13.96798052693865</v>
+        <v>-19.72513368779215</v>
       </c>
       <c r="F5">
-        <v>-0.8333915983449923</v>
+        <v>-0.4082850443719253</v>
       </c>
       <c r="G5">
-        <v>-11.96419023940945</v>
+        <v>-16.06252809266054</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-22.37064609562068</v>
       </c>
       <c r="E6">
-        <v>-13.02371671228125</v>
+        <v>-21.08256188548737</v>
       </c>
       <c r="F6">
-        <v>-0.3157530920096093</v>
+        <v>-0.748558492624295</v>
       </c>
       <c r="G6">
-        <v>-10.37690614351387</v>
+        <v>-14.77779971941726</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.95175349254108</v>
       </c>
       <c r="E7">
-        <v>-13.98602649585922</v>
+        <v>-20.07229556216818</v>
       </c>
       <c r="F7">
-        <v>-0.7865225706945963</v>
+        <v>-0.6024609905273518</v>
       </c>
       <c r="G7">
-        <v>-11.1361532785814</v>
+        <v>-14.29938285190056</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.47873390389293</v>
       </c>
       <c r="E8">
-        <v>-14.1562835331256</v>
+        <v>-20.62859142316643</v>
       </c>
       <c r="F8">
-        <v>-0.693917722000834</v>
+        <v>-0.5207930766527513</v>
       </c>
       <c r="G8">
-        <v>-10.55074620032654</v>
+        <v>-14.66115595788658</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.94895747888116</v>
       </c>
       <c r="E9">
-        <v>-13.44253715935465</v>
+        <v>-21.61436323057814</v>
       </c>
       <c r="F9">
-        <v>-0.6632225678900984</v>
+        <v>-0.5232740370241359</v>
       </c>
       <c r="G9">
-        <v>-9.045775508719396</v>
+        <v>-14.0523962913977</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-20.38315263820079</v>
       </c>
       <c r="E10">
-        <v>-13.64473805227114</v>
+        <v>-21.94315761437905</v>
       </c>
       <c r="F10">
-        <v>-0.5270861838118192</v>
+        <v>-0.4083082386592037</v>
       </c>
       <c r="G10">
-        <v>-8.915724037754668</v>
+        <v>-13.46501612800142</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.83186708938968</v>
       </c>
       <c r="E11">
-        <v>-15.66322382865807</v>
+        <v>-22.38087085501246</v>
       </c>
       <c r="F11">
-        <v>-0.4445526260012932</v>
+        <v>-0.09881195289044678</v>
       </c>
       <c r="G11">
-        <v>-8.050900294894237</v>
+        <v>-13.04824823951704</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.32151371885814</v>
       </c>
       <c r="E12">
-        <v>-15.83356237845659</v>
+        <v>-23.47683854892681</v>
       </c>
       <c r="F12">
-        <v>-0.2033469489193276</v>
+        <v>-0.09870260839327724</v>
       </c>
       <c r="G12">
-        <v>-7.942671940124383</v>
+        <v>-12.48973934376875</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.86875103839773</v>
       </c>
       <c r="E13">
-        <v>-16.70321505536361</v>
+        <v>-23.44169759062729</v>
       </c>
       <c r="F13">
-        <v>0.2643501150686761</v>
+        <v>-0.02027692453323405</v>
       </c>
       <c r="G13">
-        <v>-8.197799132108317</v>
+        <v>-12.24990356163071</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.53634254779911</v>
       </c>
       <c r="E14">
-        <v>-17.43191897878189</v>
+        <v>-23.61165122013516</v>
       </c>
       <c r="F14">
-        <v>0.1546842113468551</v>
+        <v>0.3993110458023827</v>
       </c>
       <c r="G14">
-        <v>-8.044742680191193</v>
+        <v>-11.71453868974747</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.34642785900374</v>
       </c>
       <c r="E15">
-        <v>-19.0430277619128</v>
+        <v>-24.35316619652114</v>
       </c>
       <c r="F15">
-        <v>0.9752094599440578</v>
+        <v>0.7265650435849527</v>
       </c>
       <c r="G15">
-        <v>-7.389486401603247</v>
+        <v>-11.19008537596167</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.28693738154265</v>
       </c>
       <c r="E16">
-        <v>-19.63219128725873</v>
+        <v>-25.16144446520221</v>
       </c>
       <c r="F16">
-        <v>0.6140213915058061</v>
+        <v>0.9081663725658826</v>
       </c>
       <c r="G16">
-        <v>-6.885684270891418</v>
+        <v>-11.13141919846024</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.38324763040524</v>
       </c>
       <c r="E17">
-        <v>-19.36432752123102</v>
+        <v>-26.22756951540602</v>
       </c>
       <c r="F17">
-        <v>1.658201697021861</v>
+        <v>0.9309796108389811</v>
       </c>
       <c r="G17">
-        <v>-6.936021115816037</v>
+        <v>-10.55098787015091</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.62774254264163</v>
       </c>
       <c r="E18">
-        <v>-20.80380713947122</v>
+        <v>-26.23571624014582</v>
       </c>
       <c r="F18">
-        <v>1.845089666767458</v>
+        <v>1.212152358371217</v>
       </c>
       <c r="G18">
-        <v>-7.465516390458149</v>
+        <v>-10.34445948668347</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-18.97143519099376</v>
       </c>
       <c r="E19">
-        <v>-21.48996604958744</v>
+        <v>-27.48900764956065</v>
       </c>
       <c r="F19">
-        <v>1.856439956920617</v>
+        <v>1.465056239915517</v>
       </c>
       <c r="G19">
-        <v>-6.795885723138688</v>
+        <v>-10.66084501332608</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-19.40012044363198</v>
       </c>
       <c r="E20">
-        <v>-22.13611136337188</v>
+        <v>-28.04973235813841</v>
       </c>
       <c r="F20">
-        <v>1.905674801873408</v>
+        <v>1.762271150570369</v>
       </c>
       <c r="G20">
-        <v>-7.3106623123132</v>
+        <v>-10.79843459648373</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.89132441077189</v>
       </c>
       <c r="E21">
-        <v>-24.48352284930594</v>
+        <v>-28.7978045648875</v>
       </c>
       <c r="F21">
-        <v>2.146964972430459</v>
+        <v>1.856226238130694</v>
       </c>
       <c r="G21">
-        <v>-6.789413606609412</v>
+        <v>-10.0730510317374</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.3930223418253</v>
       </c>
       <c r="E22">
-        <v>-24.06140114468095</v>
+        <v>-29.48725341137029</v>
       </c>
       <c r="F22">
-        <v>2.454325727034799</v>
+        <v>2.082993471381865</v>
       </c>
       <c r="G22">
-        <v>-6.874067566594116</v>
+        <v>-9.793670783132768</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-20.86679809253916</v>
       </c>
       <c r="E23">
-        <v>-26.75577072366069</v>
+        <v>-30.22053562201033</v>
       </c>
       <c r="F23">
-        <v>2.645150098678499</v>
+        <v>2.494851117114556</v>
       </c>
       <c r="G23">
-        <v>-6.269363318390841</v>
+        <v>-10.79160494103621</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-21.29752920208906</v>
       </c>
       <c r="E24">
-        <v>-24.2817657468422</v>
+        <v>-30.44146401918554</v>
       </c>
       <c r="F24">
-        <v>2.725241629385572</v>
+        <v>1.946594494836898</v>
       </c>
       <c r="G24">
-        <v>-6.745098644020728</v>
+        <v>-9.841756457090682</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-21.64735385206744</v>
       </c>
       <c r="E25">
-        <v>-25.55962865622266</v>
+        <v>-29.26378906875079</v>
       </c>
       <c r="F25">
-        <v>2.664699569384567</v>
+        <v>2.423651282109133</v>
       </c>
       <c r="G25">
-        <v>-6.380670480512217</v>
+        <v>-10.07830486750823</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-21.8748377423629</v>
       </c>
       <c r="E26">
-        <v>-24.28556966500865</v>
+        <v>-30.92903802288039</v>
       </c>
       <c r="F26">
-        <v>2.801100202664339</v>
+        <v>2.496784526632691</v>
       </c>
       <c r="G26">
-        <v>-7.716753691433439</v>
+        <v>-10.55107725488047</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-21.98854981799481</v>
       </c>
       <c r="E27">
-        <v>-25.76791128973145</v>
+        <v>-29.73928789650419</v>
       </c>
       <c r="F27">
-        <v>2.750125786165669</v>
+        <v>2.031770544662355</v>
       </c>
       <c r="G27">
-        <v>-6.93051236803869</v>
+        <v>-10.32303363595331</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-21.98024722723245</v>
       </c>
       <c r="E28">
-        <v>-26.11013259896511</v>
+        <v>-30.6108832887605</v>
       </c>
       <c r="F28">
-        <v>2.331947697149617</v>
+        <v>2.004096446469628</v>
       </c>
       <c r="G28">
-        <v>-6.282771027824889</v>
+        <v>-9.893318203864832</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-21.83083413205174</v>
       </c>
       <c r="E29">
-        <v>-24.75238287961534</v>
+        <v>-30.47301842607099</v>
       </c>
       <c r="F29">
-        <v>2.169597626609747</v>
+        <v>1.856381971202421</v>
       </c>
       <c r="G29">
-        <v>-7.613199826965037</v>
+        <v>-10.35263322361993</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-21.5714777446028</v>
       </c>
       <c r="E30">
-        <v>-24.8522538453805</v>
+        <v>-30.45492037969933</v>
       </c>
       <c r="F30">
-        <v>2.553587336177458</v>
+        <v>1.971293097318768</v>
       </c>
       <c r="G30">
-        <v>-5.943555979143467</v>
+        <v>-9.75142160096059</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-21.2246315235023</v>
       </c>
       <c r="E31">
-        <v>-23.65091761825567</v>
+        <v>-30.12683923055463</v>
       </c>
       <c r="F31">
-        <v>1.958562747072545</v>
+        <v>1.786376641991835</v>
       </c>
       <c r="G31">
-        <v>-7.152090491527649</v>
+        <v>-9.615149614927569</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-20.79174223388469</v>
       </c>
       <c r="E32">
-        <v>-24.66491993263119</v>
+        <v>-29.65545225720019</v>
       </c>
       <c r="F32">
-        <v>1.794441627025491</v>
+        <v>1.830969316019337</v>
       </c>
       <c r="G32">
-        <v>-5.73468372943423</v>
+        <v>-9.806088639450575</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-20.30811798585194</v>
       </c>
       <c r="E33">
-        <v>-24.38125632079072</v>
+        <v>-29.06744802120022</v>
       </c>
       <c r="F33">
-        <v>1.994517205823655</v>
+        <v>1.503900044167592</v>
       </c>
       <c r="G33">
-        <v>-6.00954177283222</v>
+        <v>-9.827021218895386</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-19.80976251770654</v>
       </c>
       <c r="E34">
-        <v>-23.44982620147106</v>
+        <v>-29.07009717849471</v>
       </c>
       <c r="F34">
-        <v>2.080480204681771</v>
+        <v>1.433545143913024</v>
       </c>
       <c r="G34">
-        <v>-6.076010906169707</v>
+        <v>-10.02147273223556</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-19.30591201411533</v>
       </c>
       <c r="E35">
-        <v>-23.27606412532274</v>
+        <v>-28.35883693695397</v>
       </c>
       <c r="F35">
-        <v>0.8953465586401574</v>
+        <v>1.603115264735694</v>
       </c>
       <c r="G35">
-        <v>-5.025826408019944</v>
+        <v>-9.427540999217072</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-18.81095004233433</v>
       </c>
       <c r="E36">
-        <v>-22.27983154295331</v>
+        <v>-29.28470609019222</v>
       </c>
       <c r="F36">
-        <v>1.844425316110413</v>
+        <v>1.384716198987605</v>
       </c>
       <c r="G36">
-        <v>-5.484836857585433</v>
+        <v>-9.651221319123469</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-18.36076936244905</v>
       </c>
       <c r="E37">
-        <v>-21.54119667603621</v>
+        <v>-27.63090285411699</v>
       </c>
       <c r="F37">
-        <v>1.778664541471771</v>
+        <v>1.553164710346884</v>
       </c>
       <c r="G37">
-        <v>-4.537004495873318</v>
+        <v>-9.258696555623162</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.96047989315413</v>
       </c>
       <c r="E38">
-        <v>-22.34960174198949</v>
+        <v>-28.13837723683856</v>
       </c>
       <c r="F38">
-        <v>2.129628899424671</v>
+        <v>1.454892171883168</v>
       </c>
       <c r="G38">
-        <v>-5.763243805801523</v>
+        <v>-8.850900245550198</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.59769172626051</v>
       </c>
       <c r="E39">
-        <v>-20.35609502822888</v>
+        <v>-27.15807129755411</v>
       </c>
       <c r="F39">
-        <v>1.896228100011883</v>
+        <v>1.532902843674408</v>
       </c>
       <c r="G39">
-        <v>-4.592426338746256</v>
+        <v>-8.695778013216568</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.29921894552848</v>
       </c>
       <c r="E40">
-        <v>-20.83790202027497</v>
+        <v>-27.11657689022183</v>
       </c>
       <c r="F40">
-        <v>1.820662768793706</v>
+        <v>1.458030027604972</v>
       </c>
       <c r="G40">
-        <v>-6.305997815328416</v>
+        <v>-9.331227297843055</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.06077914861801</v>
       </c>
       <c r="E41">
-        <v>-20.62605547772214</v>
+        <v>-26.75278193081563</v>
       </c>
       <c r="F41">
-        <v>1.479534445381647</v>
+        <v>1.530932985990551</v>
       </c>
       <c r="G41">
-        <v>-4.182766191534683</v>
+        <v>-9.04558349707812</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-16.85366447228594</v>
       </c>
       <c r="E42">
-        <v>-20.4269520610269</v>
+        <v>-25.54934449175124</v>
       </c>
       <c r="F42">
-        <v>2.325196502816801</v>
+        <v>1.49249839523546</v>
       </c>
       <c r="G42">
-        <v>-4.971119642983488</v>
+        <v>-8.887031539565804</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-16.68919023681445</v>
       </c>
       <c r="E43">
-        <v>-20.30312093928715</v>
+        <v>-25.99126921321177</v>
       </c>
       <c r="F43">
-        <v>2.061222319301488</v>
+        <v>1.474981738135861</v>
       </c>
       <c r="G43">
-        <v>-4.586027054218845</v>
+        <v>-8.805721230575765</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-16.56339592622323</v>
       </c>
       <c r="E44">
-        <v>-17.86055715750392</v>
+        <v>-24.72885745714549</v>
       </c>
       <c r="F44">
-        <v>1.731402867672448</v>
+        <v>1.400581091486021</v>
       </c>
       <c r="G44">
-        <v>-5.046891409286326</v>
+        <v>-8.923828253234802</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-16.44839786241256</v>
       </c>
       <c r="E45">
-        <v>-19.28166928516901</v>
+        <v>-24.24364505264564</v>
       </c>
       <c r="F45">
-        <v>1.706104527190951</v>
+        <v>1.423205461991281</v>
       </c>
       <c r="G45">
-        <v>-5.480943656031251</v>
+        <v>-8.271773272183333</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-16.34634096307963</v>
       </c>
       <c r="E46">
-        <v>-17.14217815482313</v>
+        <v>-23.9360348702526</v>
       </c>
       <c r="F46">
-        <v>1.754840694967257</v>
+        <v>1.270565514147027</v>
       </c>
       <c r="G46">
-        <v>-5.584762364142795</v>
+        <v>-9.031513678536216</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.26519448980309</v>
       </c>
       <c r="E47">
-        <v>-16.2865139341258</v>
+        <v>-23.37128434828202</v>
       </c>
       <c r="F47">
-        <v>1.854839551098408</v>
+        <v>1.58150150246185</v>
       </c>
       <c r="G47">
-        <v>-5.158089323404907</v>
+        <v>-9.039184212550708</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.19251229119587</v>
       </c>
       <c r="E48">
-        <v>-17.66283945385502</v>
+        <v>-23.38197154694013</v>
       </c>
       <c r="F48">
-        <v>1.833936528056165</v>
+        <v>1.549496699487288</v>
       </c>
       <c r="G48">
-        <v>-5.643114039817989</v>
+        <v>-8.547895943977323</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.12411744285651</v>
       </c>
       <c r="E49">
-        <v>-18.13774052303942</v>
+        <v>-23.5811519476935</v>
       </c>
       <c r="F49">
-        <v>1.632308588745154</v>
+        <v>1.608103693235353</v>
       </c>
       <c r="G49">
-        <v>-5.799908097648951</v>
+        <v>-9.100608074486345</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-16.08293387234828</v>
       </c>
       <c r="E50">
-        <v>-15.53523556777928</v>
+        <v>-22.64506202861995</v>
       </c>
       <c r="F50">
-        <v>1.8797220511437</v>
+        <v>1.184130345869316</v>
       </c>
       <c r="G50">
-        <v>-5.788026549708507</v>
+        <v>-9.503978185173304</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-16.06876845401662</v>
       </c>
       <c r="E51">
-        <v>-14.53479603305673</v>
+        <v>-22.12188289803978</v>
       </c>
       <c r="F51">
-        <v>1.449295721709854</v>
+        <v>1.430206823279742</v>
       </c>
       <c r="G51">
-        <v>-5.743794350758304</v>
+        <v>-9.430219230558341</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-16.06952606283594</v>
       </c>
       <c r="E52">
-        <v>-14.62993927195788</v>
+        <v>-22.16671026224171</v>
       </c>
       <c r="F52">
-        <v>1.912768940310983</v>
+        <v>1.320585651397673</v>
       </c>
       <c r="G52">
-        <v>-6.887567971303263</v>
+        <v>-9.395309527846727</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-16.11180551984811</v>
       </c>
       <c r="E53">
-        <v>-15.20139646393382</v>
+        <v>-21.60828148998584</v>
       </c>
       <c r="F53">
-        <v>1.585313649249533</v>
+        <v>1.537432356632916</v>
       </c>
       <c r="G53">
-        <v>-5.142605901917735</v>
+        <v>-9.880244859530249</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.19926684842033</v>
       </c>
       <c r="E54">
-        <v>-14.82925552693148</v>
+        <v>-21.65409153304743</v>
       </c>
       <c r="F54">
-        <v>1.913024077471045</v>
+        <v>1.406033405731247</v>
       </c>
       <c r="G54">
-        <v>-6.874703191337656</v>
+        <v>-9.908232211519248</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-16.31124469915359</v>
       </c>
       <c r="E55">
-        <v>-13.75309537832668</v>
+        <v>-20.66411730175661</v>
       </c>
       <c r="F55">
-        <v>1.546174946202062</v>
+        <v>1.615709762727858</v>
       </c>
       <c r="G55">
-        <v>-7.561134877268919</v>
+        <v>-9.991717548928589</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-16.46490894459935</v>
       </c>
       <c r="E56">
-        <v>-14.55643308186538</v>
+        <v>-21.19915650576286</v>
       </c>
       <c r="F56">
-        <v>1.817327761630035</v>
+        <v>1.235901651809479</v>
       </c>
       <c r="G56">
-        <v>-6.450400501205886</v>
+        <v>-10.41825816784491</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-16.66264930662404</v>
       </c>
       <c r="E57">
-        <v>-14.31783684334924</v>
+        <v>-20.28228995885187</v>
       </c>
       <c r="F57">
-        <v>2.254574868258532</v>
+        <v>1.408076159746551</v>
       </c>
       <c r="G57">
-        <v>-6.876424675018077</v>
+        <v>-10.25370419126989</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.88028867228759</v>
       </c>
       <c r="E58">
-        <v>-12.32858689515584</v>
+        <v>-20.09405035130102</v>
       </c>
       <c r="F58">
-        <v>1.946150489908998</v>
+        <v>1.621072613293582</v>
       </c>
       <c r="G58">
-        <v>-6.877156305582256</v>
+        <v>-10.57163574267934</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-17.11728632943474</v>
       </c>
       <c r="E59">
-        <v>-12.96908520185272</v>
+        <v>-19.87721795886575</v>
       </c>
       <c r="F59">
-        <v>1.402766324694606</v>
+        <v>1.558449694376745</v>
       </c>
       <c r="G59">
-        <v>-6.822585272912909</v>
+        <v>-10.27031650878595</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-17.37694626680443</v>
       </c>
       <c r="E60">
-        <v>-12.95864706926504</v>
+        <v>-20.08809540798094</v>
       </c>
       <c r="F60">
-        <v>1.82453124456478</v>
+        <v>1.290191194654153</v>
       </c>
       <c r="G60">
-        <v>-6.934130794313113</v>
+        <v>-10.22972259938341</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-17.6386687727383</v>
       </c>
       <c r="E61">
-        <v>-12.95127018510654</v>
+        <v>-20.35797434494206</v>
       </c>
       <c r="F61">
-        <v>2.507682528183921</v>
+        <v>1.506224443099847</v>
       </c>
       <c r="G61">
-        <v>-7.061212705929116</v>
+        <v>-10.31898814930432</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-17.88516920618787</v>
       </c>
       <c r="E62">
-        <v>-12.21430632509827</v>
+        <v>-19.27495808668964</v>
       </c>
       <c r="F62">
-        <v>1.700799662343423</v>
+        <v>1.546945327886665</v>
       </c>
       <c r="G62">
-        <v>-7.679771587214241</v>
+        <v>-10.62170112286974</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-18.12688409109291</v>
       </c>
       <c r="E63">
-        <v>-13.26916453197099</v>
+        <v>-19.50611857088519</v>
       </c>
       <c r="F63">
-        <v>1.806131547813797</v>
+        <v>1.519695353804173</v>
       </c>
       <c r="G63">
-        <v>-5.477742358494775</v>
+        <v>-10.19976547279855</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-18.35136771286876</v>
       </c>
       <c r="E64">
-        <v>-13.20272728980446</v>
+        <v>-18.95896569890841</v>
       </c>
       <c r="F64">
-        <v>2.068485444689234</v>
+        <v>1.285335304938942</v>
       </c>
       <c r="G64">
-        <v>-7.617291661251576</v>
+        <v>-10.5684543084161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-18.53396403801236</v>
       </c>
       <c r="E65">
-        <v>-12.96036788938795</v>
+        <v>-19.71895232077168</v>
       </c>
       <c r="F65">
-        <v>2.376906509569157</v>
+        <v>1.091719335147808</v>
       </c>
       <c r="G65">
-        <v>-7.174195004093363</v>
+        <v>-11.18532150093066</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.69120226376649</v>
       </c>
       <c r="E66">
-        <v>-12.34933636305898</v>
+        <v>-19.86076148432188</v>
       </c>
       <c r="F66">
-        <v>2.311510216587747</v>
+        <v>1.15223985759634</v>
       </c>
       <c r="G66">
-        <v>-8.612974648188317</v>
+        <v>-10.58701322670925</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.82104683410628</v>
       </c>
       <c r="E67">
-        <v>-12.80035878880093</v>
+        <v>-19.3107103889802</v>
       </c>
       <c r="F67">
-        <v>2.037272560951749</v>
+        <v>1.21048733989159</v>
       </c>
       <c r="G67">
-        <v>-7.731094974709563</v>
+        <v>-10.46159983004504</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.89975042930688</v>
       </c>
       <c r="E68">
-        <v>-11.3126871501711</v>
+        <v>-19.61890927299423</v>
       </c>
       <c r="F68">
-        <v>2.075238295756856</v>
+        <v>1.271707004428085</v>
       </c>
       <c r="G68">
-        <v>-6.869757236301985</v>
+        <v>-10.8311063704108</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.94422310767257</v>
       </c>
       <c r="E69">
-        <v>-11.72588776100098</v>
+        <v>-19.2844361827877</v>
       </c>
       <c r="F69">
-        <v>2.28142722598768</v>
+        <v>1.378322859372798</v>
       </c>
       <c r="G69">
-        <v>-7.547528535102514</v>
+        <v>-10.16469024280997</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.96069437616648</v>
       </c>
       <c r="E70">
-        <v>-12.62332262594506</v>
+        <v>-19.59877114908212</v>
       </c>
       <c r="F70">
-        <v>2.349028632995342</v>
+        <v>1.300572294946037</v>
       </c>
       <c r="G70">
-        <v>-7.679947046127822</v>
+        <v>-10.39162482898147</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.93218897152365</v>
       </c>
       <c r="E71">
-        <v>-13.99739296561847</v>
+        <v>-18.93743280500194</v>
       </c>
       <c r="F71">
-        <v>2.377517844712423</v>
+        <v>1.559132269116652</v>
       </c>
       <c r="G71">
-        <v>-6.22743856968151</v>
+        <v>-10.83641317491025</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.86441236282369</v>
       </c>
       <c r="E72">
-        <v>-11.80042191469323</v>
+        <v>-19.80577675292075</v>
       </c>
       <c r="F72">
-        <v>1.84758470938469</v>
+        <v>1.143293489646106</v>
       </c>
       <c r="G72">
-        <v>-7.096453463194658</v>
+        <v>-10.77792576686794</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.77223180726301</v>
       </c>
       <c r="E73">
-        <v>-13.77748121085798</v>
+        <v>-20.25419983458229</v>
       </c>
       <c r="F73">
-        <v>1.841241071814051</v>
+        <v>1.155510252102593</v>
       </c>
       <c r="G73">
-        <v>-7.472600957912189</v>
+        <v>-10.50954315054477</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.64829878947716</v>
       </c>
       <c r="E74">
-        <v>-13.85108702737866</v>
+        <v>-19.92728023902055</v>
       </c>
       <c r="F74">
-        <v>2.380223292649966</v>
+        <v>1.241234681148702</v>
       </c>
       <c r="G74">
-        <v>-8.344181524218271</v>
+        <v>-10.70572276865644</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.48573899240106</v>
       </c>
       <c r="E75">
-        <v>-12.5926467430171</v>
+        <v>-19.29185382321226</v>
       </c>
       <c r="F75">
-        <v>2.543771182454284</v>
+        <v>0.9449690795374591</v>
       </c>
       <c r="G75">
-        <v>-6.400004066461561</v>
+        <v>-10.8220189229055</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.30949360924481</v>
       </c>
       <c r="E76">
-        <v>-13.8810474114134</v>
+        <v>-19.88242117550057</v>
       </c>
       <c r="F76">
-        <v>1.753502053244333</v>
+        <v>1.417801193055417</v>
       </c>
       <c r="G76">
-        <v>-7.043461560747544</v>
+        <v>-10.42801765609468</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.1202074212313</v>
       </c>
       <c r="E77">
-        <v>-14.56051323694629</v>
+        <v>-21.26701116029379</v>
       </c>
       <c r="F77">
-        <v>1.571571034037089</v>
+        <v>1.118170763054002</v>
       </c>
       <c r="G77">
-        <v>-7.098323921424346</v>
+        <v>-10.27984425884798</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.90424204438237</v>
       </c>
       <c r="E78">
-        <v>-12.55948019938492</v>
+        <v>-20.52215417009015</v>
       </c>
       <c r="F78">
-        <v>1.50865155959005</v>
+        <v>0.9858722051528931</v>
       </c>
       <c r="G78">
-        <v>-7.224065062096944</v>
+        <v>-10.23650590719338</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.68881764957754</v>
       </c>
       <c r="E79">
-        <v>-13.99637405896674</v>
+        <v>-21.02671221555077</v>
       </c>
       <c r="F79">
-        <v>1.472647398794772</v>
+        <v>1.206683476777935</v>
       </c>
       <c r="G79">
-        <v>-6.871611141803976</v>
+        <v>-10.29110342422704</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.48148061818423</v>
       </c>
       <c r="E80">
-        <v>-15.19137042248084</v>
+        <v>-21.2331834594565</v>
       </c>
       <c r="F80">
-        <v>1.734873727090178</v>
+        <v>0.8071436543248717</v>
       </c>
       <c r="G80">
-        <v>-6.881152134048156</v>
+        <v>-10.01871835834688</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.26580342517723</v>
       </c>
       <c r="E81">
-        <v>-14.07972968002593</v>
+        <v>-21.86003747396827</v>
       </c>
       <c r="F81">
-        <v>1.551877427402934</v>
+        <v>0.7889377955461442</v>
       </c>
       <c r="G81">
-        <v>-6.496516400567933</v>
+        <v>-9.559545692049971</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.06390464098629</v>
       </c>
       <c r="E82">
-        <v>-14.54911506786898</v>
+        <v>-22.71661644641514</v>
       </c>
       <c r="F82">
-        <v>1.90613703088417</v>
+        <v>0.7777482086691285</v>
       </c>
       <c r="G82">
-        <v>-7.107924503488232</v>
+        <v>-9.870925673837201</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.88771617459012</v>
       </c>
       <c r="E83">
-        <v>-17.09270457628933</v>
+        <v>-23.50662232247526</v>
       </c>
       <c r="F83">
-        <v>1.626011339749073</v>
+        <v>0.7735218781800454</v>
       </c>
       <c r="G83">
-        <v>-6.458253115225037</v>
+        <v>-9.09014012949117</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.72465360804948</v>
       </c>
       <c r="E84">
-        <v>-17.43564591289021</v>
+        <v>-24.39300318236662</v>
       </c>
       <c r="F84">
-        <v>1.544995351020475</v>
+        <v>0.9752806995406986</v>
       </c>
       <c r="G84">
-        <v>-5.544658415480064</v>
+        <v>-9.688362329528552</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.581173299949</v>
       </c>
       <c r="E85">
-        <v>-17.13761345302339</v>
+        <v>-24.24851316220388</v>
       </c>
       <c r="F85">
-        <v>1.474961857318194</v>
+        <v>0.9352771809247049</v>
       </c>
       <c r="G85">
-        <v>-6.337461240133649</v>
+        <v>-9.371761617425891</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.47517727942461</v>
       </c>
       <c r="E86">
-        <v>-19.73670393888175</v>
+        <v>-25.5003781023063</v>
       </c>
       <c r="F86">
-        <v>1.301554738685757</v>
+        <v>0.8644202900240407</v>
       </c>
       <c r="G86">
-        <v>-5.42798154849399</v>
+        <v>-9.577061788498254</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.40077618629211</v>
       </c>
       <c r="E87">
-        <v>-19.61206674876864</v>
+        <v>-25.7306872333884</v>
       </c>
       <c r="F87">
-        <v>1.754414914122218</v>
+        <v>0.8348558574181264</v>
       </c>
       <c r="G87">
-        <v>-5.64052188266074</v>
+        <v>-9.009028453233487</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.34901426847954</v>
       </c>
       <c r="E88">
-        <v>-21.98313498291877</v>
+        <v>-27.05902904253235</v>
       </c>
       <c r="F88">
-        <v>1.782595973165457</v>
+        <v>0.2835218502390678</v>
       </c>
       <c r="G88">
-        <v>-5.858958298432931</v>
+        <v>-9.162684113893219</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.34627987142843</v>
       </c>
       <c r="E89">
-        <v>-23.06152314073535</v>
+        <v>-28.24546659017194</v>
       </c>
       <c r="F89">
-        <v>1.803790581533486</v>
+        <v>0.4911463411789443</v>
       </c>
       <c r="G89">
-        <v>-6.059401899199184</v>
+        <v>-9.109195629615215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.39377693266905</v>
       </c>
       <c r="E90">
-        <v>-24.75491429658562</v>
+        <v>-29.0410470177355</v>
       </c>
       <c r="F90">
-        <v>1.758878157688502</v>
+        <v>0.754162931976621</v>
       </c>
       <c r="G90">
-        <v>-5.394856229828043</v>
+        <v>-9.511261385359701</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.47564251314047</v>
       </c>
       <c r="E91">
-        <v>-25.42410954306911</v>
+        <v>-30.97720060818897</v>
       </c>
       <c r="F91">
-        <v>1.578907055756281</v>
+        <v>0.5595512645673218</v>
       </c>
       <c r="G91">
-        <v>-5.722679691308833</v>
+        <v>-8.963683910982089</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.61786098678244</v>
       </c>
       <c r="E92">
-        <v>-28.18595338476314</v>
+        <v>-32.42744440914541</v>
       </c>
       <c r="F92">
-        <v>1.947762492874845</v>
+        <v>0.600094050362538</v>
       </c>
       <c r="G92">
-        <v>-5.298873583007953</v>
+        <v>-9.074305790176835</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.82655180531839</v>
       </c>
       <c r="E93">
-        <v>-28.61310622401066</v>
+        <v>-34.03291071366275</v>
       </c>
       <c r="F93">
-        <v>1.704593585048245</v>
+        <v>0.3900275323192087</v>
       </c>
       <c r="G93">
-        <v>-5.387036721264284</v>
+        <v>-9.212173459159784</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.07779650377604</v>
       </c>
       <c r="E94">
-        <v>-30.38195987072475</v>
+        <v>-34.82649634842593</v>
       </c>
       <c r="F94">
-        <v>1.711699320629459</v>
+        <v>0.05300459775542422</v>
       </c>
       <c r="G94">
-        <v>-5.047136389656233</v>
+        <v>-8.635463184036587</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.38642680135658</v>
       </c>
       <c r="E95">
-        <v>-34.08532553606454</v>
+        <v>-37.53837527215633</v>
       </c>
       <c r="F95">
-        <v>1.127060802020846</v>
+        <v>0.1758804764496889</v>
       </c>
       <c r="G95">
-        <v>-5.016732339423566</v>
+        <v>-9.230427807263325</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.75950537448708</v>
       </c>
       <c r="E96">
-        <v>-36.78553911075117</v>
+        <v>-38.72688233241743</v>
       </c>
       <c r="F96">
-        <v>1.185586615763437</v>
+        <v>0.03396043116506358</v>
       </c>
       <c r="G96">
-        <v>-5.282115601488163</v>
+        <v>-8.922288849559042</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.16782814168866</v>
       </c>
       <c r="E97">
-        <v>-37.73203319885735</v>
+        <v>-40.45748848766274</v>
       </c>
       <c r="F97">
-        <v>1.796322021029845</v>
+        <v>-0.4255871543141986</v>
       </c>
       <c r="G97">
-        <v>-6.972182204741496</v>
+        <v>-8.84712622363543</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.61373025291467</v>
       </c>
       <c r="E98">
-        <v>-40.3207874427932</v>
+        <v>-42.54290284564603</v>
       </c>
       <c r="F98">
-        <v>0.2656564504628909</v>
+        <v>-0.0419768370169699</v>
       </c>
       <c r="G98">
-        <v>-4.90406454308555</v>
+        <v>-9.312638584640046</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-19.0864777850239</v>
       </c>
       <c r="E99">
-        <v>-42.27612364914316</v>
+        <v>-43.98967557127558</v>
       </c>
       <c r="F99">
-        <v>0.9791143838808547</v>
+        <v>-0.2187462989373704</v>
       </c>
       <c r="G99">
-        <v>-6.108434389181329</v>
+        <v>-9.041845891164282</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.5901881782125</v>
       </c>
       <c r="E100">
-        <v>-44.2387076781424</v>
+        <v>-45.80999532508685</v>
       </c>
       <c r="F100">
-        <v>0.6768853653368578</v>
+        <v>-0.4553031781548252</v>
       </c>
       <c r="G100">
-        <v>-5.951663505169142</v>
+        <v>-9.317183963665466</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-20.0600684022703</v>
       </c>
       <c r="E101">
-        <v>-47.29058895884269</v>
+        <v>-48.48502152734283</v>
       </c>
       <c r="F101">
-        <v>0.7845706425985852</v>
+        <v>-0.6796888551229469</v>
       </c>
       <c r="G101">
-        <v>-6.410336279089626</v>
+        <v>-9.306169778656312</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-20.57388595769787</v>
       </c>
       <c r="E102">
-        <v>-48.80398346195459</v>
+        <v>-50.16647562570888</v>
       </c>
       <c r="F102">
-        <v>0.6042400292135496</v>
+        <v>-0.834405520046019</v>
       </c>
       <c r="G102">
-        <v>-5.708073564389568</v>
+        <v>-9.47533203462199</v>
       </c>
     </row>
   </sheetData>
